--- a/Unity/Assets/Config/Excel/Skill/ElementMaterialReactionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/ElementMaterialReactionConfig.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="123">
   <si>
     <t>Id</t>
   </si>
@@ -25,34 +25,34 @@
     <t>材质类型</t>
   </si>
   <si>
-    <t>反应结果</t>
-  </si>
-  <si>
-    <t>伤害加成</t>
-  </si>
-  <si>
-    <t>反应后状态</t>
-  </si>
-  <si>
-    <t>元素计量消耗(%)</t>
+    <t>反应结果，火烧木头为例，产生结果是持续燃烧，直到木头烧完。结果会挂在材质表面。</t>
+  </si>
+  <si>
+    <t>伤害放大系数，只针对元素伤害放大, &gt; 1 为放大， &lt; 1 为减少伤害。</t>
+  </si>
+  <si>
+    <t>反应强度，0不发生反应， 一般Intensity 设置1。 攻击者不消耗元素量，反应结果是, 被攻击者元素销量 和产生的伤害都是 Min(攻击者元素量 * Intensity, 被攻击者元素销量)</t>
+  </si>
+  <si>
+    <t>反应后剩余元素每秒消耗量, 0不消耗。比如火点燃了木头，后续持续消耗剩余的木头。</t>
+  </si>
+  <si>
+    <t>反应后附加元素的持续时间，单位毫秒。如果一直燃烧，直到结束，设置一个较大值。</t>
+  </si>
+  <si>
+    <t>反应后附加的BUFF，比如持续伤害，持续周边AOE，持续蔓延。</t>
   </si>
   <si>
     <t>VFX效果名称</t>
   </si>
   <si>
-    <t>是否完全消耗元素</t>
-  </si>
-  <si>
-    <t>目标施加BuffID</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Element</t>
-  </si>
-  <si>
-    <t>Material</t>
+    <t>FromElement</t>
+  </si>
+  <si>
+    <t>ToMaterial</t>
   </si>
   <si>
     <t>Reaction</t>
@@ -61,21 +61,21 @@
     <t>DamageMultiplier</t>
   </si>
   <si>
-    <t>RemainElement</t>
-  </si>
-  <si>
-    <t>GaugeConsumption</t>
+    <t>Intensity</t>
+  </si>
+  <si>
+    <t>DaceyPerSecond</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>ApplyBuffs</t>
   </si>
   <si>
     <t>VfxName</t>
   </si>
   <si>
-    <t>IsConsumed</t>
-  </si>
-  <si>
-    <t>ApplyBuffs</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -103,15 +103,15 @@
     <t>1.5</t>
   </si>
   <si>
-    <t>100</t>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>1001</t>
   </si>
   <si>
     <t>Vfx_Burning_Grass</t>
   </si>
   <si>
-    <t>1001</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>火+冰=融化</t>
   </si>
   <si>
+    <t>1002</t>
+  </si>
+  <si>
     <t>Vfx_Melt_Ice</t>
   </si>
   <si>
-    <t>1002</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -148,24 +148,21 @@
     <t>1.2</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>Vfx_Melt_Snow</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>火+水=蒸发</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>火+水=蒸发</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>Vfx_Vaporize_Water</t>
   </si>
   <si>
@@ -175,54 +172,42 @@
     <t>1.8</t>
   </si>
   <si>
-    <t>40</t>
+    <t>1003</t>
   </si>
   <si>
     <t>Vfx_ElectroCharged_Water</t>
   </si>
   <si>
-    <t>1003</t>
-  </si>
-  <si>
     <t>雷+金属=传导</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>60</t>
+    <t>1004</t>
   </si>
   <si>
     <t>Vfx_Conductive_Metal</t>
   </si>
   <si>
-    <t>1004</t>
-  </si>
-  <si>
     <t>雷+铁丝网=传导</t>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
     <t>Vfx_Conductive_WireNet</t>
   </si>
   <si>
     <t>冰+水=冻结</t>
   </si>
   <si>
+    <t>1005</t>
+  </si>
+  <si>
     <t>Vfx_Frozen_Water</t>
   </si>
   <si>
-    <t>1005</t>
-  </si>
-  <si>
     <t>冰+雪=冻结强化</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>Vfx_Frozen_Snow</t>
   </si>
   <si>
@@ -235,151 +220,139 @@
     <t>0.8</t>
   </si>
   <si>
+    <t>Vfx_Frost_Sand</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>风+火=扩散</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>1006</t>
+  </si>
+  <si>
+    <t>Vfx_Swirl_Fire</t>
+  </si>
+  <si>
+    <t>风+水=扩散湿润</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>1007</t>
+  </si>
+  <si>
+    <t>Vfx_Swirl_Water</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>风+冰=扩散冰冻</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <t>Vfx_Swirl_Ice</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>风+雷=扩散雷电</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>Vfx_Swirl_Elec</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>岩+火=结晶</t>
+  </si>
+  <si>
+    <t>1010</t>
+  </si>
+  <si>
+    <t>Vfx_Crystallize_Fire</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>岩+水=结晶</t>
+  </si>
+  <si>
+    <t>Vfx_Crystallize_Water</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>岩+雷=结晶</t>
+  </si>
+  <si>
+    <t>Vfx_Crystallize_Elec</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>岩+冰=结晶</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>Vfx_Crystallize_Ice</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>暗+怨念=怨念强化</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>1011</t>
+  </si>
+  <si>
+    <t>Vfx_Grudge_Enhance</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>暗+肉=腐蚀</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>Vfx_Frost_Sand</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>风+火=扩散</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>Vfx_Swirl_Fire</t>
-  </si>
-  <si>
-    <t>1006</t>
-  </si>
-  <si>
-    <t>风+水=扩散湿润</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>Vfx_Swirl_Water</t>
-  </si>
-  <si>
-    <t>1007</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>风+冰=扩散冰冻</t>
-  </si>
-  <si>
-    <t>1.4</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>Vfx_Swirl_Ice</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>风+雷=扩散雷电</t>
-  </si>
-  <si>
-    <t>1.6</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>Vfx_Swirl_Elec</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>岩+火=结晶</t>
-  </si>
-  <si>
-    <t>Vfx_Crystallize_Fire</t>
-  </si>
-  <si>
-    <t>1010</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>岩+水=结晶</t>
-  </si>
-  <si>
-    <t>Vfx_Crystallize_Water</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>岩+雷=结晶</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>Vfx_Crystallize_Elec</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>岩+冰=结晶</t>
-  </si>
-  <si>
-    <t>1.25</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>Vfx_Crystallize_Ice</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>暗+怨念=怨念强化</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>Vfx_Grudge_Enhance</t>
-  </si>
-  <si>
-    <t>1011</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>暗+肉=腐蚀</t>
+    <t>1012</t>
   </si>
   <si>
     <t>Vfx_Corrupt_Meat</t>
-  </si>
-  <si>
-    <t>1012</t>
   </si>
   <si>
     <t>22</t>
@@ -439,7 +412,7 @@
       <name val="Helvetica Neue"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -448,7 +421,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="11"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -463,16 +442,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -489,13 +468,13 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -515,6 +494,7 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffa5a5a5"/>
       <rgbColor rgb="ff61d836"/>
     </indexedColors>
@@ -1555,15 +1535,15 @@
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="2" width="8.35156" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85156" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.1719" style="1" customWidth="1"/>
-    <col min="5" max="7" width="8.17188" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="7" width="8.17188" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.1719" style="1" customWidth="1"/>
     <col min="10" max="10" width="16.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.8516" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.8516" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.2188" style="1" customWidth="1"/>
+    <col min="12" max="13" width="21.5" style="1" customWidth="1"/>
     <col min="14" max="16384" width="8.35156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1693,19 +1673,19 @@
         <v>23</v>
       </c>
       <c r="I5" t="s" s="4">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="J5" t="s" s="4">
-        <v>23</v>
-      </c>
       <c r="K5" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s" s="4">
         <v>22</v>
-      </c>
-      <c r="L5" t="s" s="4">
-        <v>21</v>
-      </c>
-      <c r="M5" t="s" s="4">
-        <v>24</v>
       </c>
     </row>
     <row r="6" ht="20.05" customHeight="1">
@@ -1733,13 +1713,13 @@
         <v>25</v>
       </c>
       <c r="J6" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="K6" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="K6" t="s" s="3">
+      <c r="L6" t="s" s="3">
         <v>31</v>
-      </c>
-      <c r="L6" t="s" s="3">
-        <v>25</v>
       </c>
       <c r="M6" t="s" s="3">
         <v>32</v>
@@ -1770,16 +1750,16 @@
         <v>25</v>
       </c>
       <c r="J7" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="K7" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="K7" t="s" s="3">
+      <c r="L7" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="M7" t="s" s="3">
         <v>36</v>
-      </c>
-      <c r="L7" t="s" s="3">
-        <v>25</v>
-      </c>
-      <c r="M7" t="s" s="3">
-        <v>32</v>
       </c>
     </row>
     <row r="8" ht="20.05" customHeight="1">
@@ -1804,16 +1784,16 @@
         <v>33</v>
       </c>
       <c r="I8" t="s" s="3">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="K8" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="K8" t="s" s="3">
+      <c r="L8" t="s" s="3">
         <v>39</v>
-      </c>
-      <c r="L8" t="s" s="3">
-        <v>25</v>
       </c>
       <c r="M8" t="s" s="3">
         <v>40</v>
@@ -1841,35 +1821,35 @@
         <v>44</v>
       </c>
       <c r="I9" t="s" s="3">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J9" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="K9" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="L9" t="s" s="3">
+        <v>39</v>
+      </c>
+      <c r="M9" t="s" s="3">
         <v>45</v>
-      </c>
-      <c r="K9" t="s" s="3">
-        <v>46</v>
-      </c>
-      <c r="L9" t="s" s="3">
-        <v>47</v>
-      </c>
-      <c r="M9" t="s" s="3">
-        <v>40</v>
       </c>
     </row>
     <row r="10" ht="20.05" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" t="s" s="3">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s" s="3">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s" s="3">
         <v>48</v>
-      </c>
-      <c r="D10" t="s" s="3">
-        <v>49</v>
-      </c>
-      <c r="E10" t="s" s="3">
-        <v>25</v>
-      </c>
-      <c r="F10" t="s" s="3">
-        <v>50</v>
       </c>
       <c r="G10" t="s" s="3">
         <v>25</v>
@@ -1878,19 +1858,19 @@
         <v>33</v>
       </c>
       <c r="I10" t="s" s="3">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J10" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="K10" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="K10" t="s" s="3">
-        <v>51</v>
-      </c>
       <c r="L10" t="s" s="3">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="M10" t="s" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="20.05" customHeight="1">
@@ -1900,34 +1880,34 @@
         <v>27</v>
       </c>
       <c r="D11" t="s" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s" s="3">
         <v>41</v>
       </c>
       <c r="F11" t="s" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="I11" t="s" s="3">
+        <v>25</v>
+      </c>
+      <c r="J11" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="K11" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="L11" t="s" s="3">
         <v>53</v>
       </c>
-      <c r="I11" t="s" s="3">
-        <v>41</v>
-      </c>
-      <c r="J11" t="s" s="3">
+      <c r="M11" t="s" s="3">
         <v>54</v>
-      </c>
-      <c r="K11" t="s" s="3">
-        <v>55</v>
-      </c>
-      <c r="L11" t="s" s="3">
-        <v>47</v>
-      </c>
-      <c r="M11" t="s" s="3">
-        <v>56</v>
       </c>
     </row>
     <row r="12" ht="20.05" customHeight="1">
@@ -1937,7 +1917,7 @@
         <v>35</v>
       </c>
       <c r="D12" t="s" s="3">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s" s="3">
         <v>41</v>
@@ -1946,62 +1926,62 @@
         <v>41</v>
       </c>
       <c r="G12" t="s" s="3">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s" s="3">
         <v>33</v>
       </c>
       <c r="I12" t="s" s="3">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J12" t="s" s="3">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="K12" t="s" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L12" t="s" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="M12" t="s" s="3">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" ht="20.05" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" t="s" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s" s="3">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="3">
         <v>41</v>
       </c>
       <c r="F13" t="s" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G13" t="s" s="3">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H13" t="s" s="3">
         <v>29</v>
       </c>
       <c r="I13" t="s" s="3">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J13" t="s" s="3">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="K13" t="s" s="3">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="L13" t="s" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="M13" t="s" s="3">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="20.05" customHeight="1">
@@ -2011,13 +1991,13 @@
         <v>43</v>
       </c>
       <c r="D14" t="s" s="3">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s" s="3">
         <v>37</v>
       </c>
       <c r="F14" t="s" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G14" t="s" s="3">
         <v>27</v>
@@ -2026,19 +2006,19 @@
         <v>25</v>
       </c>
       <c r="I14" t="s" s="3">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J14" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="K14" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="K14" t="s" s="3">
-        <v>66</v>
-      </c>
       <c r="L14" t="s" s="3">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="M14" t="s" s="3">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="20.05" customHeight="1">
@@ -2048,7 +2028,7 @@
         <v>28</v>
       </c>
       <c r="D15" t="s" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s" s="3">
         <v>37</v>
@@ -2063,214 +2043,214 @@
         <v>44</v>
       </c>
       <c r="I15" t="s" s="3">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J15" t="s" s="3">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="K15" t="s" s="3">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="L15" t="s" s="3">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M15" t="s" s="3">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="20.05" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" t="s" s="3">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s" s="3">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s" s="3">
         <v>37</v>
       </c>
       <c r="F16" t="s" s="3">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G16" t="s" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H16" t="s" s="3">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I16" t="s" s="3">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J16" t="s" s="3">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="K16" t="s" s="3">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="L16" t="s" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M16" t="s" s="3">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" ht="20.05" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" t="s" s="3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s" s="3">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s" s="3">
+        <v>46</v>
+      </c>
+      <c r="F17" t="s" s="3">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s" s="3">
         <v>48</v>
       </c>
-      <c r="F17" t="s" s="3">
-        <v>25</v>
-      </c>
-      <c r="G17" t="s" s="3">
-        <v>50</v>
-      </c>
       <c r="H17" t="s" s="3">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I17" t="s" s="3">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="J17" t="s" s="3">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="K17" t="s" s="3">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="L17" t="s" s="3">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="M17" t="s" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" ht="20.05" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" t="s" s="3">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s" s="3">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s" s="3">
+        <v>46</v>
+      </c>
+      <c r="F18" t="s" s="3">
         <v>48</v>
       </c>
-      <c r="F18" t="s" s="3">
-        <v>50</v>
-      </c>
       <c r="G18" t="s" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H18" t="s" s="3">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I18" t="s" s="3">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="J18" t="s" s="3">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="K18" t="s" s="3">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="L18" t="s" s="3">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="M18" t="s" s="3">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" ht="20.05" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" t="s" s="3">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s" s="3">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s" s="3">
+        <v>46</v>
+      </c>
+      <c r="F19" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="G19" t="s" s="3">
         <v>48</v>
       </c>
-      <c r="F19" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="G19" t="s" s="3">
-        <v>50</v>
-      </c>
       <c r="H19" t="s" s="3">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I19" t="s" s="3">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="J19" t="s" s="3">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="K19" t="s" s="3">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="L19" t="s" s="3">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="M19" t="s" s="3">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" ht="20.05" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" t="s" s="3">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s" s="3">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F20" t="s" s="3">
         <v>41</v>
       </c>
       <c r="G20" t="s" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H20" t="s" s="3">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I20" t="s" s="3">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="J20" t="s" s="3">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="K20" t="s" s="3">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="L20" t="s" s="3">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="M20" t="s" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" ht="20.05" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" t="s" s="3">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s" s="3">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s" s="3">
         <v>27</v>
@@ -2285,66 +2265,66 @@
         <v>44</v>
       </c>
       <c r="I21" t="s" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J21" t="s" s="3">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="K21" t="s" s="3">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="L21" t="s" s="3">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="M21" t="s" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" ht="20.05" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" t="s" s="3">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s" s="3">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s" s="3">
         <v>27</v>
       </c>
       <c r="F22" t="s" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G22" t="s" s="3">
         <v>43</v>
       </c>
       <c r="H22" t="s" s="3">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I22" t="s" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J22" t="s" s="3">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="K22" t="s" s="3">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="L22" t="s" s="3">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="M22" t="s" s="3">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" ht="20.05" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" t="s" s="3">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s" s="3">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s" s="3">
         <v>27</v>
@@ -2356,32 +2336,32 @@
         <v>43</v>
       </c>
       <c r="H23" t="s" s="3">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I23" t="s" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J23" t="s" s="3">
-        <v>106</v>
+        <v>28</v>
       </c>
       <c r="K23" t="s" s="3">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="L23" t="s" s="3">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="M23" t="s" s="3">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" ht="20.05" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" t="s" s="3">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s" s="3">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s" s="3">
         <v>27</v>
@@ -2393,112 +2373,112 @@
         <v>43</v>
       </c>
       <c r="H24" t="s" s="3">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="I24" t="s" s="3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J24" t="s" s="3">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="K24" t="s" s="3">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="L24" t="s" s="3">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="M24" t="s" s="3">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" ht="20.05" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" t="s" s="3">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s" s="3">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F25" t="s" s="3">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="G25" t="s" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H25" t="s" s="3">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="I25" t="s" s="3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J25" t="s" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="K25" t="s" s="3">
-        <v>117</v>
+        <v>30</v>
       </c>
       <c r="L25" t="s" s="3">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="M25" t="s" s="3">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" ht="20.05" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" t="s" s="3">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s" s="3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E26" t="s" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F26" t="s" s="3">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="G26" t="s" s="3">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H26" t="s" s="3">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I26" t="s" s="3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J26" t="s" s="3">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="K26" t="s" s="3">
-        <v>121</v>
+        <v>30</v>
       </c>
       <c r="L26" t="s" s="3">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="M26" t="s" s="3">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" ht="20.05" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" t="s" s="3">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s" s="3">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E27" t="s" s="3">
         <v>25</v>
       </c>
       <c r="F27" t="s" s="3">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="3">
         <v>28</v>
@@ -2510,26 +2490,26 @@
         <v>25</v>
       </c>
       <c r="J27" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="K27" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="K27" t="s" s="3">
-        <v>125</v>
-      </c>
       <c r="L27" t="s" s="3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M27" t="s" s="3">
-        <v>32</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" ht="20.05" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" t="s" s="3">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s" s="3">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s" s="3">
         <v>25</v>
@@ -2547,13 +2527,13 @@
         <v>25</v>
       </c>
       <c r="J28" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="K28" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="K28" t="s" s="3">
+      <c r="L28" t="s" s="3">
         <v>31</v>
-      </c>
-      <c r="L28" t="s" s="3">
-        <v>25</v>
       </c>
       <c r="M28" t="s" s="3">
         <v>32</v>
@@ -2563,37 +2543,37 @@
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" t="s" s="3">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s" s="3">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s" s="3">
         <v>33</v>
       </c>
       <c r="F29" t="s" s="3">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G29" t="s" s="3">
         <v>25</v>
       </c>
       <c r="H29" t="s" s="3">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="I29" t="s" s="3">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="J29" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="K29" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="K29" t="s" s="3">
-        <v>131</v>
-      </c>
       <c r="L29" t="s" s="3">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="M29" t="s" s="3">
-        <v>47</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
